--- a/TestTable.xlsx
+++ b/TestTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MiscProjects\Peterhoff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEE4E1B3-641D-4DAE-9CF0-4FFFA3BBF0D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D4B3ECE-D0FE-468A-A321-AD544CACCAA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4950" yWindow="3495" windowWidth="21600" windowHeight="11385" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="4950" yWindow="3495" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="122">
   <si>
     <t>подпись</t>
   </si>
@@ -241,11 +241,6 @@
   </si>
   <si>
     <t>ЦГАНТД СПБ_ Ф.Р.-488. Оп.328. Д.70. Л. 2об</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Анфилада разрушенных комнат, вид из Большой столовой
-ЦГАНТД СПб. Ф. Р-488. Оп. 328. Д. 70. Л. 7
-</t>
   </si>
   <si>
     <t>ЦГАНТД СПБ_ Ф.Р.-488. Оп.328. Д.70. Л. 18</t>
@@ -570,17 +565,38 @@
 Государственный музей-заповедник «Петергоф»
 </t>
   </si>
+  <si>
+    <t xml:space="preserve">подпись без </t>
+  </si>
+  <si>
+    <t>копирайт</t>
+  </si>
+  <si>
+    <t>ЦГАНТД СПб. Ф. Р-488. Оп. 328. Д. 70. Л. 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Анфилада разрушенных комнат, вид из Большой столовой
+</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -674,9 +690,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -686,21 +702,29 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -998,6 +1022,7 @@
   <cols>
     <col min="1" max="1" width="26.85546875" customWidth="1"/>
     <col min="2" max="2" width="58.85546875" customWidth="1"/>
+    <col min="3" max="3" width="59.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -1022,50 +1047,54 @@
       <c r="B3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="11"/>
+      <c r="C3" s="14" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="4" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="11"/>
+        <v>54</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="5" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C5" s="11"/>
     </row>
     <row r="6" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" s="11"/>
     </row>
     <row r="7" spans="1:3" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C7" s="11"/>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C8" s="11"/>
     </row>
@@ -1114,28 +1143,28 @@
     </row>
     <row r="14" spans="1:3" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C14" s="11"/>
     </row>
     <row r="15" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C15" s="11"/>
     </row>
     <row r="16" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1186,10 +1215,10 @@
     </row>
     <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1205,79 +1234,79 @@
         <v>35</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="165" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="165" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="165" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="165" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="165" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="165" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="165" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="165" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="165" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -1307,10 +1336,10 @@
     </row>
     <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1326,79 +1355,79 @@
         <v>36</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="165" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="165" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="165" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="165" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="165" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="165" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="165" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="165" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="165" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1429,7 +1458,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B2" s="2"/>
     </row>
@@ -1446,7 +1475,7 @@
         <v>27</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="180" x14ac:dyDescent="0.25">
@@ -1454,7 +1483,7 @@
         <v>31</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="180" x14ac:dyDescent="0.25">
@@ -1462,7 +1491,7 @@
         <v>32</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -1475,14 +1504,14 @@
   <sheetPr>
     <tabColor theme="7" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.28515625" customWidth="1"/>
     <col min="2" max="2" width="58.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -1490,7 +1519,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -1498,15 +1527,18 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
@@ -1514,7 +1546,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -1532,14 +1564,15 @@
   <sheetPr>
     <tabColor theme="7" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.5703125" customWidth="1"/>
     <col min="2" max="2" width="58.85546875" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>15</v>
       </c>
@@ -1547,7 +1580,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
@@ -1555,15 +1588,16 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="C3" s="13"/>
+    </row>
+    <row r="4" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1571,7 +1605,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1579,7 +1613,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -1587,7 +1621,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>52</v>
       </c>
@@ -1597,6 +1631,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1635,50 +1670,50 @@
     </row>
     <row r="4" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="105" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1724,7 +1759,7 @@
         <v>28</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="150" x14ac:dyDescent="0.25">
@@ -1732,7 +1767,7 @@
         <v>29</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="105" x14ac:dyDescent="0.25">
@@ -1740,7 +1775,7 @@
         <v>30</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1789,7 +1824,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
@@ -1797,7 +1832,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1846,7 +1881,7 @@
         <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -1854,7 +1889,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -1862,7 +1897,7 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -1911,7 +1946,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -1919,7 +1954,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1968,7 +2003,7 @@
         <v>33</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="150" x14ac:dyDescent="0.25">
@@ -1976,7 +2011,7 @@
         <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
